--- a/AAAGameData/DataTables/PlayerInitTable.xlsx
+++ b/AAAGameData/DataTables/PlayerInitTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -68,12 +68,6 @@
     <t>InitWarehouseCapacity</t>
   </si>
   <si>
-    <t>ExpMultiplier</t>
-  </si>
-  <si>
-    <t>EliteSpawnRate</t>
-  </si>
-  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -123,12 +114,6 @@
   </si>
   <si>
     <t>初始仓库容量</t>
-  </si>
-  <si>
-    <t>经验倍率</t>
-  </si>
-  <si>
-    <t>精英怪概率</t>
   </si>
   <si>
     <t>描述</t>
@@ -150,14 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -613,148 +591,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1112,27 +1090,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="16.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="16.8916666666667" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,10 +1127,8 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,112 +1169,94 @@
       <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16">
+    <row r="5" ht="15" customHeight="1" spans="1:14">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
@@ -1322,7 +1278,7 @@
         <v>1001</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1332,14 +1288,8 @@
       <c r="M5" s="1">
         <v>30</v>
       </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>36</v>
+      <c r="N5" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
